--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_la_araucania.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:13</t>
+    <t xml:space="preserve">2026-09-24 01:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -573,7 +573,7 @@
         <v>-0.16</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="3">
@@ -639,7 +639,7 @@
         <v>0.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.18</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="9">
@@ -731,10 +731,10 @@
         <v>0.03</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="10">
@@ -757,7 +757,7 @@
         <v>0.07</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="11">
@@ -777,7 +777,7 @@
         <v>-0.52</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.58</v>
@@ -800,10 +800,10 @@
         <v>0.13</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>0.1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="14">
@@ -869,10 +869,10 @@
         <v>-0.39</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="16">
@@ -895,7 +895,7 @@
         <v>-0.42</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="17">
@@ -915,10 +915,10 @@
         <v>-0.7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="18">
@@ -961,10 +961,10 @@
         <v>0.22</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="20">
@@ -984,10 +984,10 @@
         <v>0.18</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="21">
@@ -1421,10 +1421,10 @@
         <v>-0.21</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="40">
@@ -1444,10 +1444,10 @@
         <v>-0.23</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="41">
@@ -1881,10 +1881,10 @@
         <v>0.25</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="60">
@@ -1904,10 +1904,10 @@
         <v>0.28</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="61">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_la_araucania.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:03</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_la_araucania.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
